--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,41 +587,44 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E2">
+        <v>0.246</v>
+      </c>
       <c r="G2">
-        <v>-0.1649956408020924</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-0.1649956408020924</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1852659110723627</v>
+        <v>0.9452736318407959</v>
       </c>
       <c r="J2">
-        <v>0.1852659110723627</v>
+        <v>0.9452736318407959</v>
       </c>
       <c r="K2">
-        <v>252.25</v>
+        <v>18.3</v>
       </c>
       <c r="L2">
-        <v>5.498038360941586</v>
+        <v>0.9104477611940298</v>
       </c>
       <c r="M2">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="N2">
-        <v>0.006125425376762275</v>
+        <v>0.04373356704645048</v>
       </c>
       <c r="O2">
-        <v>0.01998017839444995</v>
+        <v>0.2726775956284153</v>
       </c>
       <c r="P2">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="Q2">
-        <v>0.006125425376762275</v>
+        <v>0.04373356704645048</v>
       </c>
       <c r="R2">
-        <v>0.01998017839444995</v>
+        <v>0.2726775956284153</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +633,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>230.91</v>
+        <v>1.28</v>
       </c>
       <c r="V2">
-        <v>0.2806392805055907</v>
+        <v>0.0112182296231376</v>
       </c>
       <c r="W2">
-        <v>0.08505611340815121</v>
+        <v>0.1039182282793867</v>
       </c>
       <c r="X2">
-        <v>0.04954062226913222</v>
+        <v>0.08499617830552852</v>
       </c>
       <c r="Y2">
-        <v>0.03551549113901899</v>
+        <v>0.0189220499738582</v>
       </c>
       <c r="Z2">
-        <v>0.02965007994147535</v>
+        <v>0.1010608879280004</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.09553019256875661</v>
       </c>
       <c r="AB2">
-        <v>0.04522132057661047</v>
+        <v>0.08163925385622854</v>
       </c>
       <c r="AC2">
-        <v>-0.04522132057661047</v>
+        <v>0.01389093871252807</v>
       </c>
       <c r="AD2">
-        <v>84.56</v>
+        <v>22.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>84.56</v>
+        <v>22.8</v>
       </c>
       <c r="AG2">
-        <v>-146.35</v>
+        <v>21.52</v>
       </c>
       <c r="AH2">
-        <v>0.09319344031035091</v>
+        <v>0.1665449233016801</v>
       </c>
       <c r="AI2">
-        <v>0.04153935333012389</v>
+        <v>0.1039671682626539</v>
       </c>
       <c r="AJ2">
-        <v>-0.2163500628279991</v>
+        <v>0.1586786609644595</v>
       </c>
       <c r="AK2">
-        <v>-0.08109156392852196</v>
+        <v>0.09870654068434088</v>
       </c>
       <c r="AL2">
-        <v>0.357</v>
+        <v>0.717</v>
       </c>
       <c r="AM2">
-        <v>-33.043</v>
-      </c>
-      <c r="AN2">
-        <v>-14.04651162790698</v>
+        <v>0.717</v>
       </c>
       <c r="AO2">
-        <v>23.80952380952381</v>
-      </c>
-      <c r="AP2">
-        <v>24.31063122923588</v>
+        <v>26.49930264993026</v>
       </c>
       <c r="AQ2">
-        <v>-0.2572405653239718</v>
+        <v>26.49930264993026</v>
       </c>
     </row>
     <row r="3">
@@ -715,6 +712,9 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E3">
+        <v>0.246</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -722,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.930379746835443</v>
+        <v>0.9452736318407959</v>
       </c>
       <c r="J3">
-        <v>0.930379746835443</v>
+        <v>0.9452736318407959</v>
       </c>
       <c r="K3">
-        <v>14.4</v>
+        <v>18.3</v>
       </c>
       <c r="L3">
-        <v>0.9113924050632911</v>
+        <v>0.9104477611940298</v>
       </c>
       <c r="M3">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="N3">
-        <v>0.04818355640535373</v>
+        <v>0.04373356704645048</v>
       </c>
       <c r="O3">
-        <v>0.35</v>
+        <v>0.2726775956284153</v>
       </c>
       <c r="P3">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="Q3">
-        <v>0.04818355640535373</v>
+        <v>0.04373356704645048</v>
       </c>
       <c r="R3">
-        <v>0.35</v>
+        <v>0.2726775956284153</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,302 +758,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.41</v>
+        <v>1.28</v>
       </c>
       <c r="V3">
-        <v>0.0612810707456979</v>
+        <v>0.0112182296231376</v>
       </c>
       <c r="W3">
-        <v>0.08505611340815121</v>
+        <v>0.1039182282793867</v>
       </c>
       <c r="X3">
-        <v>0.05146051679157012</v>
+        <v>0.08499617830552852</v>
       </c>
       <c r="Y3">
-        <v>0.03359559661658109</v>
+        <v>0.0189220499738582</v>
       </c>
       <c r="Z3">
-        <v>0.09023312126646182</v>
+        <v>0.1010608879280004</v>
       </c>
       <c r="AA3">
-        <v>0.08395106852006257</v>
+        <v>0.09553019256875661</v>
       </c>
       <c r="AB3">
-        <v>0.04369002643725781</v>
+        <v>0.08163925385622854</v>
       </c>
       <c r="AC3">
-        <v>0.04026104208280475</v>
+        <v>0.01389093871252807</v>
       </c>
       <c r="AD3">
-        <v>29.2</v>
+        <v>22.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>29.2</v>
+        <v>22.8</v>
       </c>
       <c r="AG3">
-        <v>22.79</v>
+        <v>21.52</v>
       </c>
       <c r="AH3">
-        <v>0.2182361733931241</v>
+        <v>0.1665449233016801</v>
       </c>
       <c r="AI3">
-        <v>0.1422308816366293</v>
+        <v>0.1039671682626539</v>
       </c>
       <c r="AJ3">
-        <v>0.1788994426564095</v>
+        <v>0.1586786609644595</v>
       </c>
       <c r="AK3">
-        <v>0.1145859520337875</v>
+        <v>0.09870654068434088</v>
       </c>
       <c r="AL3">
-        <v>0.357</v>
+        <v>0.717</v>
       </c>
       <c r="AM3">
-        <v>0.357</v>
+        <v>0.717</v>
       </c>
       <c r="AO3">
-        <v>41.1764705882353</v>
+        <v>26.49930264993026</v>
       </c>
       <c r="AQ3">
-        <v>41.1764705882353</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>The National Investor Pr. J.S.C. (ADX:TNI)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>1.85</v>
-      </c>
-      <c r="L4">
-        <v>0.08008658008658008</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>15.3</v>
-      </c>
-      <c r="V4">
-        <v>0.2976653696498054</v>
-      </c>
-      <c r="W4">
-        <v>0.01796116504854369</v>
-      </c>
-      <c r="X4">
-        <v>0.04954062226913222</v>
-      </c>
-      <c r="Y4">
-        <v>-0.03157945722058853</v>
-      </c>
-      <c r="Z4">
-        <v>0.2294398092967819</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.04522132057661047</v>
-      </c>
-      <c r="AC4">
-        <v>-0.04522132057661047</v>
-      </c>
-      <c r="AD4">
-        <v>7.56</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>7.56</v>
-      </c>
-      <c r="AG4">
-        <v>-7.740000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>0.1282225237449118</v>
-      </c>
-      <c r="AI4">
-        <v>0.0607424071991001</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1772789738891434</v>
-      </c>
-      <c r="AK4">
-        <v>-0.07090509344082081</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Reem Investments PJSC (ADX:REEM)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>-1.084527220630372</v>
-      </c>
-      <c r="H5">
-        <v>-1.084527220630372</v>
-      </c>
-      <c r="I5">
-        <v>-0.8882521489971347</v>
-      </c>
-      <c r="J5">
-        <v>-0.8882521489971347</v>
-      </c>
-      <c r="K5">
-        <v>236</v>
-      </c>
-      <c r="L5">
-        <v>33.81088825214899</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>209.2</v>
-      </c>
-      <c r="V5">
-        <v>0.3137372525494901</v>
-      </c>
-      <c r="W5">
-        <v>0.1659517614795022</v>
-      </c>
-      <c r="X5">
-        <v>0.0484446519238636</v>
-      </c>
-      <c r="Y5">
-        <v>0.1175071095556386</v>
-      </c>
-      <c r="Z5">
-        <v>0.005489147530670022</v>
-      </c>
-      <c r="AA5">
-        <v>-0.004875747090279963</v>
-      </c>
-      <c r="AB5">
-        <v>0.04626468749401186</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05114043458429183</v>
-      </c>
-      <c r="AD5">
-        <v>47.8</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>47.8</v>
-      </c>
-      <c r="AG5">
-        <v>-161.4</v>
-      </c>
-      <c r="AH5">
-        <v>0.066890568150014</v>
-      </c>
-      <c r="AI5">
-        <v>0.0280203997889677</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.3193510091017016</v>
-      </c>
-      <c r="AK5">
-        <v>-0.1078372419322509</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-33.4</v>
-      </c>
-      <c r="AN5">
-        <v>-7.940199335548173</v>
-      </c>
-      <c r="AP5">
-        <v>26.81063122923588</v>
-      </c>
-      <c r="AQ5">
-        <v>0.1856287425149701</v>
+        <v>26.49930264993026</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +587,11 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.182</v>
+      </c>
       <c r="E2">
-        <v>0.246</v>
+        <v>0.16</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9452736318407959</v>
+        <v>0.9160530191458026</v>
       </c>
       <c r="J2">
-        <v>0.9452736318407959</v>
+        <v>0.9121714385562018</v>
       </c>
       <c r="K2">
-        <v>18.3</v>
+        <v>126.47</v>
       </c>
       <c r="L2">
-        <v>0.9104477611940298</v>
+        <v>0.9312960235640647</v>
       </c>
       <c r="M2">
-        <v>4.99</v>
+        <v>7.29</v>
       </c>
       <c r="N2">
-        <v>0.04373356704645048</v>
+        <v>0.005611145320197044</v>
       </c>
       <c r="O2">
-        <v>0.2726775956284153</v>
+        <v>0.05764212856803985</v>
       </c>
       <c r="P2">
-        <v>4.99</v>
+        <v>7.29</v>
       </c>
       <c r="Q2">
-        <v>0.04373356704645048</v>
+        <v>0.005611145320197044</v>
       </c>
       <c r="R2">
-        <v>0.2726775956284153</v>
+        <v>0.05764212856803985</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,67 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.28</v>
+        <v>0.952</v>
       </c>
       <c r="V2">
-        <v>0.0112182296231376</v>
-      </c>
-      <c r="W2">
-        <v>0.1039182282793867</v>
+        <v>0.0007327586206896551</v>
       </c>
       <c r="X2">
-        <v>0.08499617830552852</v>
-      </c>
-      <c r="Y2">
-        <v>0.0189220499738582</v>
+        <v>0.06883823137018506</v>
       </c>
       <c r="Z2">
-        <v>0.1010608879280004</v>
-      </c>
-      <c r="AA2">
-        <v>0.09553019256875661</v>
+        <v>0.6228786349876159</v>
       </c>
       <c r="AB2">
-        <v>0.08163925385622854</v>
-      </c>
-      <c r="AC2">
-        <v>0.01389093871252807</v>
+        <v>0.06582398582824026</v>
       </c>
       <c r="AD2">
-        <v>22.8</v>
+        <v>178.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>22.8</v>
+        <v>178.8</v>
       </c>
       <c r="AG2">
-        <v>21.52</v>
+        <v>177.848</v>
       </c>
       <c r="AH2">
-        <v>0.1665449233016801</v>
+        <v>0.1209742895805142</v>
       </c>
       <c r="AI2">
-        <v>0.1039671682626539</v>
+        <v>0.1121987951807229</v>
       </c>
       <c r="AJ2">
-        <v>0.1586786609644595</v>
+        <v>0.1204077321793198</v>
       </c>
       <c r="AK2">
-        <v>0.09870654068434088</v>
+        <v>0.1116681149883716</v>
       </c>
       <c r="AL2">
-        <v>0.717</v>
+        <v>5.941</v>
       </c>
       <c r="AM2">
-        <v>0.717</v>
+        <v>-3.059</v>
       </c>
       <c r="AO2">
-        <v>26.49930264993026</v>
+        <v>20.93923581888571</v>
       </c>
       <c r="AQ2">
-        <v>26.49930264993026</v>
+        <v>-40.66688460281138</v>
       </c>
     </row>
     <row r="3">
@@ -704,121 +695,228 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Investcorp Capital plc (ADX:ICAP)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="J3">
+        <v>0.911563696008748</v>
+      </c>
+      <c r="K3">
+        <v>117</v>
+      </c>
+      <c r="L3">
+        <v>0.9435483870967742</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0.06879834000552029</v>
+      </c>
+      <c r="AB3">
+        <v>0.06582613009157626</v>
+      </c>
+      <c r="AD3">
+        <v>163</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>163</v>
+      </c>
+      <c r="AG3">
+        <v>163</v>
+      </c>
+      <c r="AH3">
+        <v>0.1207139154262016</v>
+      </c>
+      <c r="AI3">
+        <v>0.1155209071580439</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1207139154262016</v>
+      </c>
+      <c r="AK3">
+        <v>0.1155209071580439</v>
+      </c>
+      <c r="AL3">
+        <v>5</v>
+      </c>
+      <c r="AM3">
+        <v>-4</v>
+      </c>
+      <c r="AO3">
+        <v>22.8</v>
+      </c>
+      <c r="AQ3">
+        <v>-28.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Umm Al Qaiwain General Investments Company P.S.C. (KWSE:QIC)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E3">
-        <v>0.246</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.9452736318407959</v>
-      </c>
-      <c r="J3">
-        <v>0.9452736318407959</v>
-      </c>
-      <c r="K3">
-        <v>18.3</v>
-      </c>
-      <c r="L3">
-        <v>0.9104477611940298</v>
-      </c>
-      <c r="M3">
-        <v>4.99</v>
-      </c>
-      <c r="N3">
-        <v>0.04373356704645048</v>
-      </c>
-      <c r="O3">
-        <v>0.2726775956284153</v>
-      </c>
-      <c r="P3">
-        <v>4.99</v>
-      </c>
-      <c r="Q3">
-        <v>0.04373356704645048</v>
-      </c>
-      <c r="R3">
-        <v>0.2726775956284153</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>1.28</v>
-      </c>
-      <c r="V3">
-        <v>0.0112182296231376</v>
-      </c>
-      <c r="W3">
-        <v>0.1039182282793867</v>
-      </c>
-      <c r="X3">
-        <v>0.08499617830552852</v>
-      </c>
-      <c r="Y3">
-        <v>0.0189220499738582</v>
-      </c>
-      <c r="Z3">
-        <v>0.1010608879280004</v>
-      </c>
-      <c r="AA3">
-        <v>0.09553019256875661</v>
-      </c>
-      <c r="AB3">
-        <v>0.08163925385622854</v>
-      </c>
-      <c r="AC3">
-        <v>0.01389093871252807</v>
-      </c>
-      <c r="AD3">
-        <v>22.8</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>22.8</v>
-      </c>
-      <c r="AG3">
-        <v>21.52</v>
-      </c>
-      <c r="AH3">
-        <v>0.1665449233016801</v>
-      </c>
-      <c r="AI3">
-        <v>0.1039671682626539</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1586786609644595</v>
-      </c>
-      <c r="AK3">
-        <v>0.09870654068434088</v>
-      </c>
-      <c r="AL3">
-        <v>0.717</v>
-      </c>
-      <c r="AM3">
-        <v>0.717</v>
-      </c>
-      <c r="AO3">
-        <v>26.49930264993026</v>
-      </c>
-      <c r="AQ3">
-        <v>26.49930264993026</v>
+      <c r="D4">
+        <v>0.182</v>
+      </c>
+      <c r="E4">
+        <v>0.16</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.8813559322033898</v>
+      </c>
+      <c r="J4">
+        <v>0.8813559322033898</v>
+      </c>
+      <c r="K4">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.802542372881356</v>
+      </c>
+      <c r="M4">
+        <v>7.29</v>
+      </c>
+      <c r="N4">
+        <v>0.06514745308310992</v>
+      </c>
+      <c r="O4">
+        <v>0.7697993664202745</v>
+      </c>
+      <c r="P4">
+        <v>7.29</v>
+      </c>
+      <c r="Q4">
+        <v>0.06514745308310992</v>
+      </c>
+      <c r="R4">
+        <v>0.7697993664202745</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.952</v>
+      </c>
+      <c r="V4">
+        <v>0.008507596067917783</v>
+      </c>
+      <c r="W4">
+        <v>0.04819338422391858</v>
+      </c>
+      <c r="X4">
+        <v>0.06887812273484983</v>
+      </c>
+      <c r="Y4">
+        <v>-0.02068473851093126</v>
+      </c>
+      <c r="Z4">
+        <v>0.05412347491055867</v>
+      </c>
+      <c r="AA4">
+        <v>0.04770204568388221</v>
+      </c>
+      <c r="AB4">
+        <v>0.06582184156490427</v>
+      </c>
+      <c r="AC4">
+        <v>-0.01811979588102205</v>
+      </c>
+      <c r="AD4">
+        <v>15.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>15.8</v>
+      </c>
+      <c r="AG4">
+        <v>14.848</v>
+      </c>
+      <c r="AH4">
+        <v>0.1237274862960063</v>
+      </c>
+      <c r="AI4">
+        <v>0.08652792990142387</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1171458326758608</v>
+      </c>
+      <c r="AK4">
+        <v>0.08174050911653306</v>
+      </c>
+      <c r="AL4">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AM4">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AO4">
+        <v>11.05207226354942</v>
+      </c>
+      <c r="AQ4">
+        <v>11.05207226354942</v>
       </c>
     </row>
   </sheetData>
